--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.62268630558647</v>
+        <v>4.813686524657801</v>
       </c>
       <c r="D2" t="n">
-        <v>51.66367577789266</v>
+        <v>8.395347313907557</v>
       </c>
       <c r="E2" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F2" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.46739183901659</v>
+        <v>3.650951173840197</v>
       </c>
       <c r="D3" t="n">
-        <v>44.93732174445474</v>
+        <v>7.302314783473895</v>
       </c>
       <c r="E3" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F3" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.18387630571568</v>
+        <v>4.092379899678798</v>
       </c>
       <c r="D4" t="n">
-        <v>48.62416373854558</v>
+        <v>7.901426607513658</v>
       </c>
       <c r="E4" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F4" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.56079131965287</v>
+        <v>2.853628589443591</v>
       </c>
       <c r="D5" t="n">
-        <v>28.96957647462652</v>
+        <v>4.70755617712681</v>
       </c>
       <c r="E5" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F5" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.10818982496429</v>
+        <v>3.917580846556697</v>
       </c>
       <c r="D6" t="n">
-        <v>19.55589754988576</v>
+        <v>3.177833351856436</v>
       </c>
       <c r="E6" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F6" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.86732138699398</v>
+        <v>5.828439725386522</v>
       </c>
       <c r="D7" t="n">
-        <v>44.39047195259347</v>
+        <v>7.21345169229644</v>
       </c>
       <c r="E7" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F7" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.42726858830565</v>
+        <v>4.294431145599669</v>
       </c>
       <c r="D8" t="n">
-        <v>26.34827492017656</v>
+        <v>4.281594674528692</v>
       </c>
       <c r="E8" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F8" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.76855659500285</v>
+        <v>2.887390446687963</v>
       </c>
       <c r="D9" t="n">
-        <v>17.66813589115619</v>
+        <v>2.871072082312881</v>
       </c>
       <c r="E9" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F9" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.68365381836569</v>
+        <v>2.061093745484425</v>
       </c>
       <c r="D10" t="n">
-        <v>31.45183540210844</v>
+        <v>5.110923252842621</v>
       </c>
       <c r="E10" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F10" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43875321735091</v>
+        <v>4.621297397819523</v>
       </c>
       <c r="D11" t="n">
-        <v>51.29909077081932</v>
+        <v>8.33610225025814</v>
       </c>
       <c r="E11" t="n">
-        <v>6.404346745234677</v>
+        <v>1.040706346100635</v>
       </c>
       <c r="F11" t="n">
-        <v>12.47550834529911</v>
+        <v>2.027270106111106</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
